--- a/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
@@ -1,34 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cappa\Ontology-Tradecraft\projects\project-3\assignment\src\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6317D967-1C2A-4E87-8ADF-0F3C1359F39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+  <si>
+    <t>left_iri</t>
+  </si>
+  <si>
+    <t>left_label</t>
+  </si>
+  <si>
+    <t>left_shape</t>
+  </si>
+  <si>
+    <t>left_axioms</t>
+  </si>
+  <si>
+    <t>right_iri</t>
+  </si>
+  <si>
+    <t>right_label</t>
+  </si>
+  <si>
+    <t>right_shape</t>
+  </si>
+  <si>
+    <t>right_axioms</t>
+  </si>
+  <si>
+    <t>left_definition</t>
+  </si>
+  <si>
+    <t>right_definition</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+  </si>
+  <si>
+    <t>temporal region</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://purl.obolibrary.org/obo/BFO_0000003</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
+  </si>
+  <si>
+    <t>Arbitrary Period</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#Element</t>
+  </si>
+  <si>
+    <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+  </si>
+  <si>
+    <t>A PeriodOfTime is an Element whose spatial extent is everywhere, but whose temporal extent is limited.</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#ParticularPeriod</t>
+  </si>
+  <si>
+    <t>Particular Period</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
+  </si>
+  <si>
+    <t>A PeriodOfTime that is a specific, contiguous extent of time.
+IMPORTANT NOTE: The URI of a ParticularPeriod shall be encoded in UTC (Coordinated Universal Time) and as follows:
+http://iso8601.iso.org/20070118T153000
+Where the content after the / is encoded without punctuation and without the trailing "Z". In the example above, the punctuated equivalent would be "2007-01-18T15:30:00Z"
+The reason behind using a URI is that receiving systems can resolve the periods of time and de-duplicate.
+Examples:
+Tuesday 28th August 2018
+2016
+December 1944</t>
+  </si>
+  <si>
+    <t>Period Of Time</t>
+  </si>
+  <si>
+    <t>http://ies.data.gov.uk/ontology/ies4#RecurringPeriod</t>
+  </si>
+  <si>
+    <t>Recurring Period</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#ArbitraryPeriod</t>
+  </si>
+  <si>
+    <t>A PeriodOfTime that is composed of regularly recurring periods of time.
+ISO8601 is used to represent these periods (recurrentPeriodRepresentation property), using the blanking technique (e.g. blanking the date to give a daily time). The recurrence can be limited using the startsIn and endsIn properties
+Examples:
+Every Tuesday from 28th August 2018 to 2 October 2018
+13:00 to 14:00 on every day from 27th June 2016 to 2 October 2024</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +149,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,64 +451,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="85" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>left_iri</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>left_label</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>left_shape</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>left_axioms</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>right_iri</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>right_label</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>right_shape</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>right_axioms</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>left_definition</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>right_definition</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
@@ -1,136 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cappa\Ontology-Tradecraft\projects\project-3\assignment\src\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6317D967-1C2A-4E87-8ADF-0F3C1359F39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
-  <si>
-    <t>left_iri</t>
-  </si>
-  <si>
-    <t>left_label</t>
-  </si>
-  <si>
-    <t>left_shape</t>
-  </si>
-  <si>
-    <t>left_axioms</t>
-  </si>
-  <si>
-    <t>right_iri</t>
-  </si>
-  <si>
-    <t>right_label</t>
-  </si>
-  <si>
-    <t>right_shape</t>
-  </si>
-  <si>
-    <t>right_axioms</t>
-  </si>
-  <si>
-    <t>left_definition</t>
-  </si>
-  <si>
-    <t>right_definition</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
-  </si>
-  <si>
-    <t>temporal region</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://purl.obolibrary.org/obo/BFO_0000003</t>
-  </si>
-  <si>
-    <t>http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
-  </si>
-  <si>
-    <t>Arbitrary Period</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#Element</t>
-  </si>
-  <si>
-    <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
-  </si>
-  <si>
-    <t>A PeriodOfTime is an Element whose spatial extent is everywhere, but whose temporal extent is limited.</t>
-  </si>
-  <si>
-    <t>http://ies.data.gov.uk/ontology/ies4#ParticularPeriod</t>
-  </si>
-  <si>
-    <t>Particular Period</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
-  </si>
-  <si>
-    <t>A PeriodOfTime that is a specific, contiguous extent of time.
-IMPORTANT NOTE: The URI of a ParticularPeriod shall be encoded in UTC (Coordinated Universal Time) and as follows:
-http://iso8601.iso.org/20070118T153000
-Where the content after the / is encoded without punctuation and without the trailing "Z". In the example above, the punctuated equivalent would be "2007-01-18T15:30:00Z"
-The reason behind using a URI is that receiving systems can resolve the periods of time and de-duplicate.
-Examples:
-Tuesday 28th August 2018
-2016
-December 1944</t>
-  </si>
-  <si>
-    <t>Period Of Time</t>
-  </si>
-  <si>
-    <t>http://ies.data.gov.uk/ontology/ies4#RecurringPeriod</t>
-  </si>
-  <si>
-    <t>Recurring Period</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#ArbitraryPeriod</t>
-  </si>
-  <si>
-    <t>A PeriodOfTime that is composed of regularly recurring periods of time.
-ISO8601 is used to represent these periods (recurrentPeriodRepresentation property), using the blanking technique (e.g. blanking the date to give a daily time). The recurrence can be limited using the startsIn and endsIn properties
-Examples:
-Every Tuesday from 28th August 2018 to 2 October 2018
-13:00 to 14:00 on every day from 27th June 2016 to 2 October 2024</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -149,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -451,156 +408,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="39.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="85" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="68.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255.6328125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>left_iri</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>left_label</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>left_shape</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>left_axioms</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>right_iri</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>right_label</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>right_shape</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>right_axioms</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>left_definition</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>right_definition</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://purl.obolibrary.org/obo/BFO_0000003</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arbitrary Period</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#Element</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>A PeriodOfTime is an Element whose spatial extent is everywhere, but whose temporal extent is limited.</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://purl.obolibrary.org/obo/BFO_0000003</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ParticularPeriod</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Particular Period</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>A PeriodOfTime that is a specific, contiguous extent of time.
+IMPORTANT NOTE: The URI of a ParticularPeriod shall be encoded in UTC (Coordinated Universal Time) and as follows:
+http://iso8601.iso.org/20070118T153000
+Where the content after the / is encoded without punctuation and without the trailing "Z". In the example above, the punctuated equivalent would be "2007-01-18T15:30:00Z"
+The reason behind using a URI is that receiving systems can resolve the periods of time and de-duplicate.
+Examples:
+Tuesday 28th August 2018
+2016
+December 1944</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://purl.obolibrary.org/obo/BFO_0000003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#PeriodOfTime</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Period Of Time</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#Element</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>A PeriodOfTime is an Element whose spatial extent is everywhere, but whose temporal extent is limited.</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://purl.obolibrary.org/obo/BFO_0000003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RecurringPeriod</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Recurring Period</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf http://ies.data.gov.uk/ontology/ies4#ArbitraryPeriod</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>A PeriodOfTime that is composed of regularly recurring periods of time.
+ISO8601 is used to represent these periods (recurrentPeriodRepresentation property), using the blanking technique (e.g. blanking the date to give a daily time). The recurrence can be limited using the startsIn and endsIn properties
+Examples:
+Every Tuesday from 28th August 2018 to 2 October 2018
+13:00 to 14:00 on every day from 27th June 2016 to 2 October 2024</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cappa\Ontology-Tradecraft\projects\project-3\assignment\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F204E4-D2AB-4B0A-9584-189DEBED409B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0E66C8-9821-4BD2-915B-35EAB0D718B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,12 +128,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -148,8 +154,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,14 +464,14 @@
   <cols>
     <col min="1" max="1" width="39.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="85" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" customWidth="1"/>
+    <col min="4" max="4" width="85" customWidth="1"/>
     <col min="5" max="5" width="46.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="91.6328125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="68.1796875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="255.6328125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" customWidth="1"/>
+    <col min="8" max="8" width="91.6328125" customWidth="1"/>
+    <col min="9" max="9" width="68.1796875" customWidth="1"/>
+    <col min="10" max="10" width="255.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -499,107 +506,107 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>26</v>
       </c>
     </row>
